--- a/artfynd/A 9683-2023 artfynd.xlsx
+++ b/artfynd/A 9683-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9683-2023 artfynd.xlsx
+++ b/artfynd/A 9683-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87534959</v>
+        <v>87534894</v>
       </c>
       <c r="B2" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689264.9391468526</v>
+        <v>689274</v>
       </c>
       <c r="R2" t="n">
-        <v>6687680.910338431</v>
+        <v>6687669</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -757,19 +752,9 @@
           <t>2020-06-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-06-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -805,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87535273</v>
+        <v>87534959</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,27 +801,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -850,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689276.2119664144</v>
+        <v>689265</v>
       </c>
       <c r="R3" t="n">
-        <v>6687665.099541753</v>
+        <v>6687681</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,19 +867,9 @@
           <t>2020-06-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-06-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -931,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87534894</v>
+        <v>87535165</v>
       </c>
       <c r="B4" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,7 +935,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -980,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689274.0206215099</v>
+        <v>689281</v>
       </c>
       <c r="R4" t="n">
-        <v>6687668.960597485</v>
+        <v>6687658</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1013,19 +982,9 @@
           <t>2020-06-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-06-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1061,15 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87534834</v>
+        <v>126307015</v>
       </c>
       <c r="B5" t="n">
-        <v>103178</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1077,46 +1031,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221141</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Snuggsund, Upl</t>
+          <t>Sandvik, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689254.9495117667</v>
+        <v>689265</v>
       </c>
       <c r="R5" t="n">
-        <v>6687700.762620326</v>
+        <v>6687664</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1140,27 +1085,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Förekomst längs väg nr 1120 O om vägbanan i innerslänt.</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,78 +1105,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Daniel Tooke</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Daniel Tooke</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>87535165</v>
+        <v>126306997</v>
       </c>
       <c r="B6" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>220164</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Snuggsund, Upl</t>
+          <t>Sandvik, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>689281.0652716568</v>
+        <v>689280</v>
       </c>
       <c r="R6" t="n">
-        <v>6687657.898736372</v>
+        <v>6687653</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1270,27 +1182,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Förekomst längs väg nr 1120 O om vägbanan i innerslänt.</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,15 +1202,348 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Daniel Tooke</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Tooke</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>87534834</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Snuggsund, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>689255</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6687701</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-06-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-06-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Förekomst längs väg nr 1120 O om vägbanan i innerslänt.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>87535193</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Snuggsund, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>689242</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6687718</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-06-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Förekomst längs väg nr 1120 V om vägbanan i ytterslänt.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>87535273</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Snuggsund, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>689276</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6687665</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-06-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-06-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Förekomst längs väg nr 1120 O om vägbanan i innerslänt.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 9683-2023 artfynd.xlsx
+++ b/artfynd/A 9683-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87534894</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87534959</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87535165</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126307015</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1211,6 +1236,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126306997</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87534834</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87535193</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,8 +1588,23 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87535273</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>